--- a/docs/Automation Testing 1200.xlsx
+++ b/docs/Automation Testing 1200.xlsx
@@ -603,7 +603,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Automated End-to-End Test Execution Report | Build v2.4.0-prod-sync | Date: 2026-08-24</t>
+          <t>Automated End-to-End Test Execution Report | Build v2.4.0-prod-sync | Date: 2026-08-25</t>
         </is>
       </c>
     </row>
